--- a/output/quickfixopen1_all_markets_daily.xlsx
+++ b/output/quickfixopen1_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixopen1 daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-30); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-31 15:45 UTC.</t>
+          <t>quickfixopen1 daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-30); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-31 17:02 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixopen1_all_markets_daily.xlsx
+++ b/output/quickfixopen1_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F14" t="n">
         <v>4</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -1274,11 +1274,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -1370,11 +1370,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
@@ -1418,11 +1418,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1508,11 +1508,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1553,11 +1553,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1598,11 +1598,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1643,11 +1643,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1691,11 +1691,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixopen1 daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-30); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-07-31 17:02 UTC.</t>
+          <t>quickfixopen1 daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 19:43 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixopen1_all_markets_daily.xlsx
+++ b/output/quickfixopen1_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixopen1 daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 19:43 UTC.</t>
+          <t>quickfixopen1 daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 22:59 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixopen1_all_markets_daily.xlsx
+++ b/output/quickfixopen1_all_markets_daily.xlsx
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixopen1 daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-01 22:59 UTC.</t>
+          <t>quickfixopen1 daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-02 00:09 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixopen1_all_markets_daily.xlsx
+++ b/output/quickfixopen1_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F9" t="n">
         <v>2</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F10" t="n">
         <v>4</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F12" t="n">
         <v>3</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F13" t="n">
         <v>2</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F14" t="n">
         <v>4</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F15" t="n">
         <v>1</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F16" t="n">
         <v>1</v>
@@ -1274,11 +1274,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -1370,11 +1370,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
@@ -1418,11 +1418,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1508,11 +1508,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1553,11 +1553,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1598,11 +1598,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1643,11 +1643,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1691,11 +1691,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixopen1 daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-07-31); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-02 00:09 UTC.</t>
+          <t>quickfixopen1 daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-04); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-05 13:32 UTC.</t>
         </is>
       </c>
     </row>

--- a/output/quickfixopen1_all_markets_daily.xlsx
+++ b/output/quickfixopen1_all_markets_daily.xlsx
@@ -554,11 +554,11 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F2" t="n">
         <v>9</v>
@@ -576,7 +576,7 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
         <v>100</v>
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -879,7 +879,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B9" t="inlineStr"/>
@@ -890,17 +890,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -918,16 +918,16 @@
         <v>100</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4.93</v>
+        <v>5.53</v>
       </c>
       <c r="N9" s="3" t="n">
-        <v>104933.65</v>
+        <v>105533.93</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -938,17 +938,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -966,10 +966,10 @@
         <v>100</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>4.9</v>
+        <v>4.93</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>104900.16</v>
+        <v>104933.65</v>
       </c>
     </row>
     <row r="11">
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -1023,7 +1023,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1062,16 +1062,16 @@
         <v>100</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4.2</v>
+        <v>4.33</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>104196.44</v>
+        <v>104330.45</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>EURO_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -1082,17 +1082,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1110,37 +1110,37 @@
         <v>100</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2.83</v>
+        <v>4.2</v>
       </c>
       <c r="N13" s="3" t="n">
-        <v>102829.25</v>
+        <v>104196.44</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>EURO_Futures</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-01-02</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>143</v>
+        <v>73</v>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -1155,40 +1155,40 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="N14" s="3" t="n">
-        <v>102624.91</v>
+        <v>102829.25</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-02</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="F15" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1203,13 +1203,13 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="N15" s="3" t="n">
-        <v>102501.7</v>
+        <v>102624.91</v>
       </c>
     </row>
     <row r="16">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -1254,10 +1254,10 @@
         <v>100</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>2.04</v>
+        <v>2.39</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>102037.7</v>
+        <v>102388.55</v>
       </c>
     </row>
     <row r="17">
@@ -1274,11 +1274,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -1370,11 +1370,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
@@ -1418,11 +1418,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1508,11 +1508,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1553,11 +1553,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1598,11 +1598,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1643,11 +1643,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1691,11 +1691,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixopen1 daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-04); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-05 13:32 UTC.</t>
+          <t>quickfixopen1 daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-06); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-07 13:34 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5034,11 +5034,11 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Japanese_Yen_Futures</t>
+          <t>Gold_Futures_COMEX</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5047,48 +5047,31 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="F46" t="n">
-        <v>1</v>
+          <t>2026-08-06</t>
+        </is>
       </c>
       <c r="G46" t="n">
-        <v>0.006417</v>
+        <v>4305.3</v>
       </c>
       <c r="H46" t="n">
-        <v>0.006454</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0.006405</v>
+        <v>4363.8</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>exit_open</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>0.3243</v>
-      </c>
-      <c r="M46" s="2" t="n">
-        <v>0.3243</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N46" t="n">
-        <v>100000</v>
+        <v>121665.67</v>
       </c>
       <c r="O46" t="n">
-        <v>100324.32</v>
+        <v>121665.67</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Live_Cattle_Futures_CME</t>
+          <t>Japanese_Yen_Futures</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -5101,25 +5084,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F47" t="n">
         <v>1</v>
       </c>
       <c r="G47" t="n">
-        <v>239.06</v>
+        <v>0.006417</v>
       </c>
       <c r="H47" t="n">
-        <v>239.73</v>
+        <v>0.006454</v>
       </c>
       <c r="J47" t="n">
-        <v>237.5</v>
+        <v>0.006405</v>
       </c>
       <c r="K47" t="inlineStr">
         <is>
@@ -5127,16 +5110,16 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.3284</v>
+        <v>0.3243</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>2.3284</v>
+        <v>0.3243</v>
       </c>
       <c r="N47" t="n">
         <v>100000</v>
       </c>
       <c r="O47" t="n">
-        <v>102328.36</v>
+        <v>100324.32</v>
       </c>
     </row>
     <row r="48">
@@ -5146,7 +5129,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5155,25 +5138,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F48" t="n">
         <v>1</v>
       </c>
       <c r="G48" t="n">
-        <v>251.58</v>
+        <v>239.06</v>
       </c>
       <c r="H48" t="n">
-        <v>251.91</v>
+        <v>239.73</v>
       </c>
       <c r="J48" t="n">
-        <v>251.52</v>
+        <v>237.5</v>
       </c>
       <c r="K48" t="inlineStr">
         <is>
@@ -5181,16 +5164,16 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0.1818</v>
+        <v>2.3284</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.1818</v>
+        <v>2.3284</v>
       </c>
       <c r="N48" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O48" t="n">
         <v>102328.36</v>
-      </c>
-      <c r="O48" t="n">
-        <v>102514.41</v>
       </c>
     </row>
     <row r="49">
@@ -5200,7 +5183,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5209,25 +5192,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F49" t="n">
         <v>1</v>
       </c>
       <c r="G49" t="n">
-        <v>255.38</v>
+        <v>251.58</v>
       </c>
       <c r="H49" t="n">
-        <v>256.63</v>
+        <v>251.91</v>
       </c>
       <c r="J49" t="n">
-        <v>252.97</v>
+        <v>251.52</v>
       </c>
       <c r="K49" t="inlineStr">
         <is>
@@ -5235,16 +5218,16 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>1.928</v>
+        <v>0.1818</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>1.928</v>
+        <v>0.1818</v>
       </c>
       <c r="N49" t="n">
+        <v>102328.36</v>
+      </c>
+      <c r="O49" t="n">
         <v>102514.41</v>
-      </c>
-      <c r="O49" t="n">
-        <v>104490.89</v>
       </c>
     </row>
     <row r="50">
@@ -5254,34 +5237,34 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F50" t="n">
         <v>1</v>
       </c>
       <c r="G50" t="n">
-        <v>235.2</v>
+        <v>255.38</v>
       </c>
       <c r="H50" t="n">
-        <v>234.36</v>
+        <v>256.63</v>
       </c>
       <c r="J50" t="n">
-        <v>238.1</v>
+        <v>252.97</v>
       </c>
       <c r="K50" t="inlineStr">
         <is>
@@ -5289,26 +5272,26 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.4524</v>
+        <v>1.928</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>3.4524</v>
+        <v>1.928</v>
       </c>
       <c r="N50" t="n">
+        <v>102514.41</v>
+      </c>
+      <c r="O50" t="n">
         <v>104490.89</v>
-      </c>
-      <c r="O50" t="n">
-        <v>108098.31</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>NY_Copper_Futures</t>
+          <t>Live_Cattle_Futures_CME</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5317,25 +5300,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-02-05</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-02-06</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F51" t="n">
         <v>1</v>
       </c>
       <c r="G51" t="n">
-        <v>5.7714</v>
+        <v>235.2</v>
       </c>
       <c r="H51" t="n">
-        <v>5.6849</v>
+        <v>234.36</v>
       </c>
       <c r="J51" t="n">
-        <v>5.732</v>
+        <v>238.1</v>
       </c>
       <c r="K51" t="inlineStr">
         <is>
@@ -5343,16 +5326,16 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>-0.4555</v>
-      </c>
-      <c r="M51" s="10" t="n">
-        <v>-0.4555</v>
+        <v>3.4524</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>3.4524</v>
       </c>
       <c r="N51" t="n">
-        <v>100000</v>
+        <v>104490.89</v>
       </c>
       <c r="O51" t="n">
-        <v>99544.50999999999</v>
+        <v>108098.31</v>
       </c>
     </row>
     <row r="52">
@@ -5362,7 +5345,7 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5371,12 +5354,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-02-13</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-06</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5386,10 +5369,10 @@
         <v>5.7714</v>
       </c>
       <c r="H52" t="n">
-        <v>5.6774</v>
+        <v>5.6849</v>
       </c>
       <c r="J52" t="n">
-        <v>5.7855</v>
+        <v>5.732</v>
       </c>
       <c r="K52" t="inlineStr">
         <is>
@@ -5397,16 +5380,16 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="M52" s="2" t="n">
-        <v>0.15</v>
+        <v>-0.4555</v>
+      </c>
+      <c r="M52" s="10" t="n">
+        <v>-0.4555</v>
       </c>
       <c r="N52" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O52" t="n">
         <v>99544.50999999999</v>
-      </c>
-      <c r="O52" t="n">
-        <v>99693.83</v>
       </c>
     </row>
     <row r="53">
@@ -5416,7 +5399,7 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5425,25 +5408,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-02-13</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-02-17</t>
         </is>
       </c>
       <c r="F53" t="n">
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>5.3133</v>
+        <v>5.7714</v>
       </c>
       <c r="H53" t="n">
-        <v>5.2459</v>
+        <v>5.6774</v>
       </c>
       <c r="J53" t="n">
-        <v>5.485</v>
+        <v>5.7855</v>
       </c>
       <c r="K53" t="inlineStr">
         <is>
@@ -5451,16 +5434,16 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.5475</v>
+        <v>0.15</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2.5475</v>
+        <v>0.15</v>
       </c>
       <c r="N53" t="n">
+        <v>99544.50999999999</v>
+      </c>
+      <c r="O53" t="n">
         <v>99693.83</v>
-      </c>
-      <c r="O53" t="n">
-        <v>102233.5</v>
       </c>
     </row>
     <row r="54">
@@ -5470,34 +5453,34 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-04-15</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="F54" t="n">
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>6.0956</v>
+        <v>5.3133</v>
       </c>
       <c r="H54" t="n">
-        <v>6.1481</v>
+        <v>5.2459</v>
       </c>
       <c r="J54" t="n">
-        <v>6.0755</v>
+        <v>5.485</v>
       </c>
       <c r="K54" t="inlineStr">
         <is>
@@ -5505,26 +5488,26 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0.3829</v>
+        <v>2.5475</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.3829</v>
+        <v>2.5475</v>
       </c>
       <c r="N54" t="n">
+        <v>99693.83</v>
+      </c>
+      <c r="O54" t="n">
         <v>102233.5</v>
-      </c>
-      <c r="O54" t="n">
-        <v>102624.91</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -5533,25 +5516,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="F55" t="n">
         <v>1</v>
       </c>
       <c r="G55" t="n">
-        <v>3.305</v>
+        <v>6.0956</v>
       </c>
       <c r="H55" t="n">
-        <v>3.354</v>
+        <v>6.1481</v>
       </c>
       <c r="J55" t="n">
-        <v>3.267</v>
+        <v>6.0755</v>
       </c>
       <c r="K55" t="inlineStr">
         <is>
@@ -5559,16 +5542,16 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0.7755</v>
+        <v>0.3829</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.7755</v>
+        <v>0.3829</v>
       </c>
       <c r="N55" t="n">
-        <v>100000</v>
+        <v>102233.5</v>
       </c>
       <c r="O55" t="n">
-        <v>100775.51</v>
+        <v>102624.91</v>
       </c>
     </row>
     <row r="56">
@@ -5578,7 +5561,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -5587,12 +5570,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -5602,10 +5585,10 @@
         <v>3.305</v>
       </c>
       <c r="H56" t="n">
-        <v>3.356</v>
+        <v>3.354</v>
       </c>
       <c r="J56" t="n">
-        <v>3.219</v>
+        <v>3.267</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
@@ -5613,16 +5596,16 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.6863</v>
+        <v>0.7755</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>1.6863</v>
+        <v>0.7755</v>
       </c>
       <c r="N56" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O56" t="n">
         <v>100775.51</v>
-      </c>
-      <c r="O56" t="n">
-        <v>102474.86</v>
       </c>
     </row>
     <row r="57">
@@ -5632,34 +5615,34 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F57" t="n">
         <v>1</v>
       </c>
       <c r="G57" t="n">
-        <v>2.69</v>
+        <v>3.305</v>
       </c>
       <c r="H57" t="n">
-        <v>2.665</v>
+        <v>3.356</v>
       </c>
       <c r="J57" t="n">
-        <v>2.732</v>
+        <v>3.219</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5667,26 +5650,26 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.68</v>
+        <v>1.6863</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1.68</v>
+        <v>1.6863</v>
       </c>
       <c r="N57" t="n">
+        <v>100775.51</v>
+      </c>
+      <c r="O57" t="n">
         <v>102474.86</v>
-      </c>
-      <c r="O57" t="n">
-        <v>104196.44</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -5695,25 +5678,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H58" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="J58" t="n">
-        <v>1403</v>
+        <v>2.732</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5721,16 +5704,16 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>2.5059</v>
+        <v>1.68</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>2.5059</v>
+        <v>1.68</v>
       </c>
       <c r="N58" t="n">
-        <v>100000</v>
+        <v>102474.86</v>
       </c>
       <c r="O58" t="n">
-        <v>102505.88</v>
+        <v>104196.44</v>
       </c>
     </row>
     <row r="59">
@@ -5740,7 +5723,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -5749,25 +5732,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H59" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="J59" t="n">
-        <v>1185</v>
+        <v>1403</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5775,53 +5758,53 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.3684</v>
+        <v>2.5059</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2.3684</v>
+        <v>2.5059</v>
       </c>
       <c r="N59" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O59" t="n">
         <v>102505.88</v>
-      </c>
-      <c r="O59" t="n">
-        <v>104933.65</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H60" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="J60" t="n">
-        <v>2031.1</v>
+        <v>1185</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5829,16 +5812,16 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>1.8385</v>
+        <v>2.3684</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>1.8385</v>
+        <v>2.3684</v>
       </c>
       <c r="N60" t="n">
-        <v>100000</v>
+        <v>102505.88</v>
       </c>
       <c r="O60" t="n">
-        <v>101838.49</v>
+        <v>104933.65</v>
       </c>
     </row>
     <row r="61">
@@ -5848,34 +5831,34 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>1641.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H61" t="n">
-        <v>1621</v>
+        <v>2113.7</v>
       </c>
       <c r="J61" t="n">
-        <v>1651</v>
+        <v>2031.1</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5883,16 +5866,16 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0.4634</v>
+        <v>1.8385</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.4634</v>
+        <v>1.8385</v>
       </c>
       <c r="N61" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O61" t="n">
         <v>101838.49</v>
-      </c>
-      <c r="O61" t="n">
-        <v>102310.42</v>
       </c>
     </row>
     <row r="62">
@@ -5902,7 +5885,7 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -5911,25 +5894,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F62" t="n">
         <v>1</v>
       </c>
       <c r="G62" t="n">
-        <v>1581.5</v>
+        <v>1641.5</v>
       </c>
       <c r="H62" t="n">
-        <v>1547.6</v>
+        <v>1621</v>
       </c>
       <c r="J62" t="n">
-        <v>1618.8</v>
+        <v>1651</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
@@ -5937,16 +5920,16 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>1.1003</v>
+        <v>0.4634</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>1.1003</v>
+        <v>0.4634</v>
       </c>
       <c r="N62" t="n">
+        <v>101838.49</v>
+      </c>
+      <c r="O62" t="n">
         <v>102310.42</v>
-      </c>
-      <c r="O62" t="n">
-        <v>103436.14</v>
       </c>
     </row>
     <row r="63">
@@ -5956,7 +5939,7 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -5965,25 +5948,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>1559</v>
+        <v>1581.5</v>
       </c>
       <c r="H63" t="n">
-        <v>1539.5</v>
+        <v>1547.6</v>
       </c>
       <c r="J63" t="n">
-        <v>1586.6</v>
+        <v>1618.8</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5991,53 +5974,53 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.4154</v>
+        <v>1.1003</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1.4154</v>
+        <v>1.1003</v>
       </c>
       <c r="N63" t="n">
+        <v>102310.42</v>
+      </c>
+      <c r="O63" t="n">
         <v>103436.14</v>
-      </c>
-      <c r="O63" t="n">
-        <v>104900.16</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>27907</v>
+        <v>1559</v>
       </c>
       <c r="H64" t="n">
-        <v>27965.76</v>
+        <v>1539.5</v>
       </c>
       <c r="J64" t="n">
-        <v>27760</v>
+        <v>1586.6</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6045,26 +6028,26 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>2.5017</v>
+        <v>1.4154</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>2.5017</v>
+        <v>1.4154</v>
       </c>
       <c r="N64" t="n">
-        <v>100000</v>
+        <v>103436.14</v>
       </c>
       <c r="O64" t="n">
-        <v>102501.7</v>
+        <v>104900.16</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -6073,25 +6056,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-04-29</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>7206.55</v>
+        <v>1769.6</v>
       </c>
       <c r="H65" t="n">
-        <v>7223.26</v>
+        <v>1798.4</v>
       </c>
       <c r="J65" t="n">
-        <v>7172.5</v>
+        <v>1752.2</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -6099,22 +6082,22 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>2.0377</v>
+        <v>0.6042</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2.0377</v>
+        <v>0.6042</v>
       </c>
       <c r="N65" t="n">
-        <v>100000</v>
+        <v>104900.16</v>
       </c>
       <c r="O65" t="n">
-        <v>102037.7</v>
+        <v>105533.93</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B66" t="n">
@@ -6127,25 +6110,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>6957.43</v>
+        <v>27907</v>
       </c>
       <c r="H66" t="n">
-        <v>6965.7</v>
+        <v>27965.76</v>
       </c>
       <c r="J66" t="n">
-        <v>6914.11</v>
+        <v>27760</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -6153,22 +6136,22 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>5.2382</v>
+        <v>2.5017</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>5.2382</v>
+        <v>2.5017</v>
       </c>
       <c r="N66" t="n">
         <v>100000</v>
       </c>
       <c r="O66" t="n">
-        <v>105238.21</v>
+        <v>102501.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B67" t="n">
@@ -6181,25 +6164,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F67" t="n">
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>6982.4</v>
+        <v>29892.8</v>
       </c>
       <c r="H67" t="n">
-        <v>6988.83</v>
+        <v>30074.01</v>
       </c>
       <c r="J67" t="n">
-        <v>7002</v>
+        <v>29569.5</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -6207,26 +6190,26 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>-3.0482</v>
-      </c>
-      <c r="M67" s="10" t="n">
-        <v>-3.0482</v>
+        <v>1.7841</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>1.7841</v>
       </c>
       <c r="N67" t="n">
-        <v>105238.21</v>
+        <v>102501.7</v>
       </c>
       <c r="O67" t="n">
-        <v>102030.33</v>
+        <v>104330.45</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -6235,25 +6218,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F68" t="n">
         <v>1</v>
       </c>
       <c r="G68" t="n">
-        <v>6982.4</v>
+        <v>7206.55</v>
       </c>
       <c r="H68" t="n">
-        <v>6992.85</v>
+        <v>7223.26</v>
       </c>
       <c r="J68" t="n">
-        <v>6947.27</v>
+        <v>7172.5</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
@@ -6261,26 +6244,26 @@
         </is>
       </c>
       <c r="L68" t="n">
-        <v>3.3617</v>
+        <v>2.0377</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3.3617</v>
+        <v>2.0377</v>
       </c>
       <c r="N68" t="n">
-        <v>102030.33</v>
+        <v>100000</v>
       </c>
       <c r="O68" t="n">
-        <v>105460.3</v>
+        <v>102037.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -6289,25 +6272,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>6982.4</v>
+        <v>7773</v>
       </c>
       <c r="H69" t="n">
-        <v>6991.93</v>
+        <v>7820.26</v>
       </c>
       <c r="J69" t="n">
-        <v>6985.45</v>
+        <v>7756.75</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6315,16 +6298,16 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="M69" s="10" t="n">
-        <v>-0.32</v>
+        <v>0.3438</v>
+      </c>
+      <c r="M69" s="2" t="n">
+        <v>0.3438</v>
       </c>
       <c r="N69" t="n">
-        <v>105460.3</v>
+        <v>102037.7</v>
       </c>
       <c r="O69" t="n">
-        <v>105122.79</v>
+        <v>102388.55</v>
       </c>
     </row>
     <row r="70">
@@ -6334,7 +6317,7 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -6343,25 +6326,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H70" t="n">
-        <v>6986.84</v>
+        <v>6965.7</v>
       </c>
       <c r="J70" t="n">
-        <v>6976.48</v>
+        <v>6914.11</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6369,16 +6352,16 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>1.3333</v>
+        <v>5.2382</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>1.3333</v>
+        <v>5.2382</v>
       </c>
       <c r="N70" t="n">
-        <v>105122.79</v>
+        <v>100000</v>
       </c>
       <c r="O70" t="n">
-        <v>106524.42</v>
+        <v>105238.21</v>
       </c>
     </row>
     <row r="71">
@@ -6388,34 +6371,34 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H71" t="n">
-        <v>6770.77</v>
+        <v>6988.83</v>
       </c>
       <c r="J71" t="n">
-        <v>6769.03</v>
+        <v>7002</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6423,26 +6406,26 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-1.0736</v>
+        <v>-3.0482</v>
       </c>
       <c r="M71" s="10" t="n">
-        <v>-1.0736</v>
+        <v>-3.0482</v>
       </c>
       <c r="N71" t="n">
-        <v>106524.42</v>
+        <v>105238.21</v>
       </c>
       <c r="O71" t="n">
-        <v>105380.74</v>
+        <v>102030.33</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -6451,25 +6434,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H72" t="n">
-        <v>88.001</v>
+        <v>6992.85</v>
       </c>
       <c r="J72" t="n">
-        <v>87.31999999999999</v>
+        <v>6947.27</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6477,53 +6460,53 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>-0.6453</v>
-      </c>
-      <c r="M72" s="10" t="n">
-        <v>-0.6453</v>
+        <v>3.3617</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>3.3617</v>
       </c>
       <c r="N72" t="n">
-        <v>100000</v>
+        <v>102030.33</v>
       </c>
       <c r="O72" t="n">
-        <v>99354.69</v>
+        <v>105460.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>73.84399999999999</v>
+        <v>6982.4</v>
       </c>
       <c r="H73" t="n">
-        <v>71.999</v>
+        <v>6991.93</v>
       </c>
       <c r="J73" t="n">
-        <v>75.565</v>
+        <v>6985.45</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6531,26 +6514,26 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0.9328</v>
-      </c>
-      <c r="M73" s="2" t="n">
-        <v>0.9328</v>
+        <v>-0.32</v>
+      </c>
+      <c r="M73" s="10" t="n">
+        <v>-0.32</v>
       </c>
       <c r="N73" t="n">
-        <v>99354.69</v>
+        <v>105460.3</v>
       </c>
       <c r="O73" t="n">
-        <v>100281.46</v>
+        <v>105122.79</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -6559,25 +6542,25 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F74" t="n">
         <v>1</v>
       </c>
       <c r="G74" t="n">
-        <v>15</v>
+        <v>6982.4</v>
       </c>
       <c r="H74" t="n">
-        <v>15.26</v>
+        <v>6986.84</v>
       </c>
       <c r="J74" t="n">
-        <v>15</v>
+        <v>6976.48</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6585,53 +6568,53 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" s="4" t="n">
-        <v>0</v>
+        <v>1.3333</v>
+      </c>
+      <c r="M74" s="2" t="n">
+        <v>1.3333</v>
       </c>
       <c r="N74" t="n">
-        <v>100000</v>
+        <v>105122.79</v>
       </c>
       <c r="O74" t="n">
-        <v>100000</v>
+        <v>106524.42</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>20.89</v>
+        <v>6794.4</v>
       </c>
       <c r="H75" t="n">
-        <v>21.07</v>
+        <v>6770.77</v>
       </c>
       <c r="J75" t="n">
-        <v>21.08</v>
+        <v>6769.03</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6639,22 +6622,22 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-1.0556</v>
+        <v>-1.0736</v>
       </c>
       <c r="M75" s="10" t="n">
-        <v>-1.0556</v>
+        <v>-1.0736</v>
       </c>
       <c r="N75" t="n">
-        <v>100000</v>
+        <v>106524.42</v>
       </c>
       <c r="O75" t="n">
-        <v>98944.44</v>
+        <v>105380.74</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B76" t="n">
@@ -6667,25 +6650,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>0.8614000000000001</v>
+        <v>86.081</v>
       </c>
       <c r="H76" t="n">
-        <v>0.8637</v>
+        <v>88.001</v>
       </c>
       <c r="J76" t="n">
-        <v>0.8594000000000001</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6693,22 +6676,22 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0.8696</v>
-      </c>
-      <c r="M76" s="2" t="n">
-        <v>0.8696</v>
+        <v>-0.6453</v>
+      </c>
+      <c r="M76" s="10" t="n">
+        <v>-0.6453</v>
       </c>
       <c r="N76" t="n">
         <v>100000</v>
       </c>
       <c r="O76" t="n">
-        <v>100869.57</v>
+        <v>99354.69</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B77" t="n">
@@ -6716,30 +6699,30 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>0.8614000000000001</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H77" t="n">
-        <v>0.8658</v>
+        <v>71.999</v>
       </c>
       <c r="J77" t="n">
-        <v>0.8602</v>
+        <v>75.565</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6747,76 +6730,76 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0.2727</v>
+        <v>0.9328</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>0.2727</v>
+        <v>0.9328</v>
       </c>
       <c r="N77" t="n">
-        <v>100869.57</v>
+        <v>99354.69</v>
       </c>
       <c r="O77" t="n">
-        <v>101144.66</v>
+        <v>100281.46</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>0.8467</v>
+        <v>15</v>
       </c>
       <c r="H78" t="n">
-        <v>0.8436</v>
+        <v>15.26</v>
       </c>
       <c r="J78" t="n">
-        <v>0.8498</v>
+        <v>15</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>1</v>
-      </c>
-      <c r="M78" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="M78" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="N78" t="n">
-        <v>101144.66</v>
+        <v>100000</v>
       </c>
       <c r="O78" t="n">
-        <v>102156.11</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -6829,25 +6812,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>116.5</v>
+        <v>20.89</v>
       </c>
       <c r="H79" t="n">
-        <v>116.79</v>
+        <v>21.07</v>
       </c>
       <c r="J79" t="n">
-        <v>116.15</v>
+        <v>21.08</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6855,26 +6838,26 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>1.2069</v>
-      </c>
-      <c r="M79" s="2" t="n">
-        <v>1.2069</v>
+        <v>-1.0556</v>
+      </c>
+      <c r="M79" s="10" t="n">
+        <v>-1.0556</v>
       </c>
       <c r="N79" t="n">
         <v>100000</v>
       </c>
       <c r="O79" t="n">
-        <v>101206.9</v>
+        <v>98944.44</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -6883,25 +6866,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>118.02</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>118.16</v>
+        <v>0.8637</v>
       </c>
       <c r="J80" t="n">
-        <v>117.9</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6909,26 +6892,26 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.8571</v>
+        <v>0.8696</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>0.8571</v>
+        <v>0.8696</v>
       </c>
       <c r="N80" t="n">
-        <v>101206.9</v>
+        <v>100000</v>
       </c>
       <c r="O80" t="n">
-        <v>102074.38</v>
+        <v>100869.57</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -6937,25 +6920,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>118.08</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>118.16</v>
+        <v>0.8658</v>
       </c>
       <c r="J81" t="n">
-        <v>117.87</v>
+        <v>0.8602</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6963,26 +6946,26 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>2.625</v>
+        <v>0.2727</v>
       </c>
       <c r="M81" s="2" t="n">
-        <v>2.625</v>
+        <v>0.2727</v>
       </c>
       <c r="N81" t="n">
-        <v>102074.38</v>
+        <v>100869.57</v>
       </c>
       <c r="O81" t="n">
-        <v>104753.84</v>
+        <v>101144.66</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -6991,79 +6974,79 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G82" t="n">
-        <v>97.81399999999999</v>
+        <v>0.8467</v>
       </c>
       <c r="H82" t="n">
-        <v>97.569</v>
+        <v>0.8436</v>
       </c>
       <c r="J82" t="n">
-        <v>98</v>
+        <v>0.8498</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0.7592</v>
+        <v>1</v>
       </c>
       <c r="M82" s="2" t="n">
-        <v>0.7592</v>
+        <v>1</v>
       </c>
       <c r="N82" t="n">
-        <v>100000</v>
+        <v>101144.66</v>
       </c>
       <c r="O82" t="n">
-        <v>100759.18</v>
+        <v>102156.11</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>97.714</v>
+        <v>116.5</v>
       </c>
       <c r="H83" t="n">
-        <v>97.46899999999999</v>
+        <v>116.79</v>
       </c>
       <c r="J83" t="n">
-        <v>97.905</v>
+        <v>116.15</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7071,26 +7054,26 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0.7796</v>
+        <v>1.2069</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>0.7796</v>
+        <v>1.2069</v>
       </c>
       <c r="N83" t="n">
-        <v>100759.18</v>
+        <v>100000</v>
       </c>
       <c r="O83" t="n">
-        <v>101544.69</v>
+        <v>101206.9</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -7099,25 +7082,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>99.376</v>
+        <v>118.02</v>
       </c>
       <c r="H84" t="n">
-        <v>99.571</v>
+        <v>118.16</v>
       </c>
       <c r="J84" t="n">
-        <v>99.095</v>
+        <v>117.9</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7125,26 +7108,26 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>1.441</v>
+        <v>0.8571</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>1.441</v>
+        <v>0.8571</v>
       </c>
       <c r="N84" t="n">
-        <v>101544.69</v>
+        <v>101206.9</v>
       </c>
       <c r="O84" t="n">
-        <v>103007.98</v>
+        <v>102074.38</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -7153,25 +7136,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F85" t="n">
         <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>99.246</v>
+        <v>118.08</v>
       </c>
       <c r="H85" t="n">
-        <v>99.501</v>
+        <v>118.16</v>
       </c>
       <c r="J85" t="n">
-        <v>98.87</v>
+        <v>117.87</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
@@ -7179,16 +7162,16 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.4745</v>
+        <v>2.625</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>1.4745</v>
+        <v>2.625</v>
       </c>
       <c r="N85" t="n">
-        <v>103007.98</v>
+        <v>102074.38</v>
       </c>
       <c r="O85" t="n">
-        <v>104526.84</v>
+        <v>104753.84</v>
       </c>
     </row>
     <row r="86">
@@ -7198,34 +7181,34 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>100.066</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H86" t="n">
-        <v>100.201</v>
+        <v>97.569</v>
       </c>
       <c r="J86" t="n">
-        <v>100.045</v>
+        <v>98</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7233,16 +7216,16 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0.1556</v>
+        <v>0.7592</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>0.1556</v>
+        <v>0.7592</v>
       </c>
       <c r="N86" t="n">
-        <v>104526.84</v>
+        <v>100000</v>
       </c>
       <c r="O86" t="n">
-        <v>104689.44</v>
+        <v>100759.18</v>
       </c>
     </row>
     <row r="87">
@@ -7252,34 +7235,34 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>100.066</v>
+        <v>97.714</v>
       </c>
       <c r="H87" t="n">
-        <v>100.316</v>
+        <v>97.46899999999999</v>
       </c>
       <c r="J87" t="n">
-        <v>99.45999999999999</v>
+        <v>97.905</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7287,16 +7270,16 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>2.424</v>
+        <v>0.7796</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>2.424</v>
+        <v>0.7796</v>
       </c>
       <c r="N87" t="n">
-        <v>104689.44</v>
+        <v>100759.18</v>
       </c>
       <c r="O87" t="n">
-        <v>107227.11</v>
+        <v>101544.69</v>
       </c>
     </row>
     <row r="88">
@@ -7306,7 +7289,7 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -7315,25 +7298,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H88" t="n">
-        <v>100.361</v>
+        <v>99.571</v>
       </c>
       <c r="J88" t="n">
-        <v>100.15</v>
+        <v>99.095</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7341,16 +7324,16 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>-0.2847</v>
-      </c>
-      <c r="M88" s="10" t="n">
-        <v>-0.2847</v>
+        <v>1.441</v>
+      </c>
+      <c r="M88" s="2" t="n">
+        <v>1.441</v>
       </c>
       <c r="N88" t="n">
-        <v>107227.11</v>
+        <v>101544.69</v>
       </c>
       <c r="O88" t="n">
-        <v>106921.79</v>
+        <v>103007.98</v>
       </c>
     </row>
     <row r="89">
@@ -7360,7 +7343,7 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -7369,25 +7352,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>100.621</v>
+        <v>99.246</v>
       </c>
       <c r="H89" t="n">
-        <v>100.911</v>
+        <v>99.501</v>
       </c>
       <c r="J89" t="n">
-        <v>100.7</v>
+        <v>98.87</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7395,16 +7378,16 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>-0.2724</v>
-      </c>
-      <c r="M89" s="10" t="n">
-        <v>-0.2724</v>
+        <v>1.4745</v>
+      </c>
+      <c r="M89" s="2" t="n">
+        <v>1.4745</v>
       </c>
       <c r="N89" t="n">
-        <v>106921.79</v>
+        <v>103007.98</v>
       </c>
       <c r="O89" t="n">
-        <v>106630.52</v>
+        <v>104526.84</v>
       </c>
     </row>
     <row r="90">
@@ -7414,7 +7397,7 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -7423,25 +7406,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H90" t="n">
-        <v>101.526</v>
+        <v>100.201</v>
       </c>
       <c r="J90" t="n">
-        <v>101.295</v>
+        <v>100.045</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7449,16 +7432,16 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>1.0087</v>
+        <v>0.1556</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>1.0087</v>
+        <v>0.1556</v>
       </c>
       <c r="N90" t="n">
-        <v>106630.52</v>
+        <v>104526.84</v>
       </c>
       <c r="O90" t="n">
-        <v>107706.09</v>
+        <v>104689.44</v>
       </c>
     </row>
     <row r="91">
@@ -7468,7 +7451,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -7477,25 +7460,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H91" t="n">
-        <v>101.491</v>
+        <v>100.316</v>
       </c>
       <c r="J91" t="n">
-        <v>101.29</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7503,26 +7486,26 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.5125</v>
+        <v>2.424</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>1.5125</v>
+        <v>2.424</v>
       </c>
       <c r="N91" t="n">
-        <v>107706.09</v>
+        <v>104689.44</v>
       </c>
       <c r="O91" t="n">
-        <v>109335.15</v>
+        <v>107227.11</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -7531,25 +7514,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F92" t="n">
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>121.72</v>
+        <v>100.066</v>
       </c>
       <c r="H92" t="n">
-        <v>123.03</v>
+        <v>100.361</v>
       </c>
       <c r="J92" t="n">
-        <v>113.29</v>
+        <v>100.15</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7557,69 +7540,285 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>6.4351</v>
-      </c>
-      <c r="M92" s="2" t="n">
-        <v>6.4351</v>
+        <v>-0.2847</v>
+      </c>
+      <c r="M92" s="10" t="n">
+        <v>-0.2847</v>
       </c>
       <c r="N92" t="n">
-        <v>100000</v>
+        <v>107227.11</v>
       </c>
       <c r="O92" t="n">
-        <v>106435.11</v>
+        <v>106921.79</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>8</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="n">
+        <v>100.621</v>
+      </c>
+      <c r="H93" t="n">
+        <v>100.911</v>
+      </c>
+      <c r="J93" t="n">
+        <v>100.7</v>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>-0.2724</v>
+      </c>
+      <c r="M93" s="10" t="n">
+        <v>-0.2724</v>
+      </c>
+      <c r="N93" t="n">
+        <v>106921.79</v>
+      </c>
+      <c r="O93" t="n">
+        <v>106630.52</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>9</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H94" t="n">
+        <v>101.526</v>
+      </c>
+      <c r="J94" t="n">
+        <v>101.295</v>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>1.0087</v>
+      </c>
+      <c r="M94" s="2" t="n">
+        <v>1.0087</v>
+      </c>
+      <c r="N94" t="n">
+        <v>106630.52</v>
+      </c>
+      <c r="O94" t="n">
+        <v>107706.09</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>10</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H95" t="n">
+        <v>101.491</v>
+      </c>
+      <c r="J95" t="n">
+        <v>101.29</v>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>1.5125</v>
+      </c>
+      <c r="M95" s="2" t="n">
+        <v>1.5125</v>
+      </c>
+      <c r="N95" t="n">
+        <v>107706.09</v>
+      </c>
+      <c r="O95" t="n">
+        <v>109335.15</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B93" t="n">
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H96" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="J96" t="n">
+        <v>113.29</v>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>6.4351</v>
+      </c>
+      <c r="M96" s="2" t="n">
+        <v>6.4351</v>
+      </c>
+      <c r="N96" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O96" t="n">
+        <v>106435.11</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
         <v>2</v>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E97" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="F93" t="n">
-        <v>1</v>
-      </c>
-      <c r="G93" t="n">
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="n">
         <v>130.16</v>
       </c>
-      <c r="H93" t="n">
+      <c r="H97" t="n">
         <v>130.94</v>
       </c>
-      <c r="J93" t="n">
+      <c r="J97" t="n">
         <v>124.86</v>
       </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>exit_open</t>
-        </is>
-      </c>
-      <c r="L93" t="n">
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
         <v>6.7949</v>
       </c>
-      <c r="M93" s="2" t="n">
+      <c r="M97" s="2" t="n">
         <v>6.7949</v>
       </c>
-      <c r="N93" t="n">
+      <c r="N97" t="n">
         <v>106435.11</v>
       </c>
-      <c r="O93" t="n">
+      <c r="O97" t="n">
         <v>113667.24</v>
       </c>
     </row>

--- a/output/quickfixopen1_all_markets_daily.xlsx
+++ b/output/quickfixopen1_all_markets_daily.xlsx
@@ -554,17 +554,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -576,16 +576,16 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>100</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>21.67</v>
+        <v>21.81</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>121665.67</v>
+        <v>121811.25</v>
       </c>
     </row>
     <row r="3">
@@ -602,11 +602,11 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
@@ -650,11 +650,11 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
@@ -698,11 +698,11 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F5" t="n">
         <v>4</v>
@@ -746,11 +746,11 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F6" t="n">
         <v>10</v>
@@ -794,11 +794,11 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F7" t="n">
         <v>4</v>
@@ -842,11 +842,11 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F8" t="n">
         <v>2</v>
@@ -890,11 +890,11 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
@@ -912,7 +912,7 @@
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>100</v>
@@ -938,11 +938,11 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F10" t="n">
         <v>2</v>
@@ -960,7 +960,7 @@
         <v>0</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
         <v>100</v>
@@ -986,11 +986,11 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
@@ -1034,11 +1034,11 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F12" t="n">
         <v>2</v>
@@ -1082,11 +1082,11 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F13" t="n">
         <v>3</v>
@@ -1130,11 +1130,11 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F14" t="n">
         <v>2</v>
@@ -1178,11 +1178,11 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F15" t="n">
         <v>4</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
         <v>75</v>
@@ -1226,11 +1226,11 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F16" t="n">
         <v>2</v>
@@ -1274,11 +1274,11 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F17" t="n">
         <v>1</v>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F18" t="n">
         <v>1</v>
@@ -1370,11 +1370,11 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F19" t="n">
         <v>2</v>
@@ -1418,11 +1418,11 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F21" t="n">
         <v>0</v>
@@ -1508,11 +1508,11 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F22" t="n">
         <v>0</v>
@@ -1553,11 +1553,11 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1598,11 +1598,11 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1643,11 +1643,11 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1691,11 +1691,11 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
@@ -2543,7 +2543,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>quickfixopen1 daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-06); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-07 13:34 UTC.</t>
+          <t>quickfixopen1 daily (exit = the open of the price bar that follows the entry bar), starting capital 100,000, risk 1.39%/trade, fees 0.0. obsolete = last bar &gt; 30d before newest (2026-08-07); a position still open on an obsolete market's last bar is flattened at that bar's close (data_end). generated 2026-08-08 17:31 UTC.</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O97"/>
+  <dimension ref="A1:O100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5050,22 +5050,39 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
       <c r="G46" t="n">
         <v>4305.3</v>
       </c>
       <c r="H46" t="n">
         <v>4363.8</v>
       </c>
+      <c r="J46" t="n">
+        <v>4298.3</v>
+      </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>open_at_end</t>
-        </is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>0.1197</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>0.1197</v>
       </c>
       <c r="N46" t="n">
         <v>121665.67</v>
       </c>
       <c r="O46" t="n">
-        <v>121665.67</v>
+        <v>121811.25</v>
       </c>
     </row>
     <row r="47">
@@ -5557,11 +5574,11 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>NY_Natural_Gas_Futures</t>
+          <t>NY_Copper_Futures</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -5570,42 +5587,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2026-06-26</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>1</v>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G56" t="n">
-        <v>3.305</v>
+        <v>6.7286</v>
       </c>
       <c r="H56" t="n">
-        <v>3.354</v>
-      </c>
-      <c r="J56" t="n">
-        <v>3.267</v>
+        <v>6.7656</v>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>exit_open</t>
-        </is>
-      </c>
-      <c r="L56" t="n">
-        <v>0.7755</v>
-      </c>
-      <c r="M56" s="2" t="n">
-        <v>0.7755</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N56" t="n">
-        <v>100000</v>
+        <v>102624.91</v>
       </c>
       <c r="O56" t="n">
-        <v>100775.51</v>
+        <v>102624.91</v>
       </c>
     </row>
     <row r="57">
@@ -5615,7 +5615,7 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -5624,12 +5624,12 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -5639,10 +5639,10 @@
         <v>3.305</v>
       </c>
       <c r="H57" t="n">
-        <v>3.356</v>
+        <v>3.354</v>
       </c>
       <c r="J57" t="n">
-        <v>3.219</v>
+        <v>3.267</v>
       </c>
       <c r="K57" t="inlineStr">
         <is>
@@ -5650,16 +5650,16 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>1.6863</v>
+        <v>0.7755</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>1.6863</v>
+        <v>0.7755</v>
       </c>
       <c r="N57" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O57" t="n">
         <v>100775.51</v>
-      </c>
-      <c r="O57" t="n">
-        <v>102474.86</v>
       </c>
     </row>
     <row r="58">
@@ -5669,34 +5669,34 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F58" t="n">
         <v>1</v>
       </c>
       <c r="G58" t="n">
-        <v>2.69</v>
+        <v>3.305</v>
       </c>
       <c r="H58" t="n">
-        <v>2.665</v>
+        <v>3.356</v>
       </c>
       <c r="J58" t="n">
-        <v>2.732</v>
+        <v>3.219</v>
       </c>
       <c r="K58" t="inlineStr">
         <is>
@@ -5704,26 +5704,26 @@
         </is>
       </c>
       <c r="L58" t="n">
-        <v>1.68</v>
+        <v>1.6863</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>1.68</v>
+        <v>1.6863</v>
       </c>
       <c r="N58" t="n">
+        <v>100775.51</v>
+      </c>
+      <c r="O58" t="n">
         <v>102474.86</v>
-      </c>
-      <c r="O58" t="n">
-        <v>104196.44</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>NY_Palladium_Futures</t>
+          <t>NY_Natural_Gas_Futures</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -5732,25 +5732,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F59" t="n">
         <v>1</v>
       </c>
       <c r="G59" t="n">
-        <v>1360.4</v>
+        <v>2.69</v>
       </c>
       <c r="H59" t="n">
-        <v>1343.4</v>
+        <v>2.665</v>
       </c>
       <c r="J59" t="n">
-        <v>1403</v>
+        <v>2.732</v>
       </c>
       <c r="K59" t="inlineStr">
         <is>
@@ -5758,16 +5758,16 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.5059</v>
+        <v>1.68</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>2.5059</v>
+        <v>1.68</v>
       </c>
       <c r="N59" t="n">
-        <v>100000</v>
+        <v>102474.86</v>
       </c>
       <c r="O59" t="n">
-        <v>102505.88</v>
+        <v>104196.44</v>
       </c>
     </row>
     <row r="60">
@@ -5777,7 +5777,7 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -5786,25 +5786,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="F60" t="n">
         <v>1</v>
       </c>
       <c r="G60" t="n">
-        <v>1167</v>
+        <v>1360.4</v>
       </c>
       <c r="H60" t="n">
-        <v>1159.4</v>
+        <v>1343.4</v>
       </c>
       <c r="J60" t="n">
-        <v>1185</v>
+        <v>1403</v>
       </c>
       <c r="K60" t="inlineStr">
         <is>
@@ -5812,53 +5812,53 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2.3684</v>
+        <v>2.5059</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2.3684</v>
+        <v>2.5059</v>
       </c>
       <c r="N60" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O60" t="n">
         <v>102505.88</v>
-      </c>
-      <c r="O60" t="n">
-        <v>104933.65</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F61" t="n">
         <v>1</v>
       </c>
       <c r="G61" t="n">
-        <v>2084.6</v>
+        <v>1167</v>
       </c>
       <c r="H61" t="n">
-        <v>2113.7</v>
+        <v>1159.4</v>
       </c>
       <c r="J61" t="n">
-        <v>2031.1</v>
+        <v>1185</v>
       </c>
       <c r="K61" t="inlineStr">
         <is>
@@ -5866,70 +5866,53 @@
         </is>
       </c>
       <c r="L61" t="n">
-        <v>1.8385</v>
+        <v>2.3684</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>1.8385</v>
+        <v>2.3684</v>
       </c>
       <c r="N61" t="n">
-        <v>100000</v>
+        <v>102505.88</v>
       </c>
       <c r="O61" t="n">
-        <v>101838.49</v>
+        <v>104933.65</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NY_Platinum_Futures</t>
+          <t>NY_Palladium_Futures</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2026-06-24</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>1</v>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G62" t="n">
-        <v>1641.5</v>
+        <v>1386.6</v>
       </c>
       <c r="H62" t="n">
-        <v>1621</v>
-      </c>
-      <c r="J62" t="n">
-        <v>1651</v>
+        <v>1412.1</v>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>exit_open</t>
-        </is>
-      </c>
-      <c r="L62" t="n">
-        <v>0.4634</v>
-      </c>
-      <c r="M62" s="2" t="n">
-        <v>0.4634</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N62" t="n">
-        <v>101838.49</v>
+        <v>104933.65</v>
       </c>
       <c r="O62" t="n">
-        <v>102310.42</v>
+        <v>104933.65</v>
       </c>
     </row>
     <row r="63">
@@ -5939,34 +5922,34 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-05-08</t>
         </is>
       </c>
       <c r="F63" t="n">
         <v>1</v>
       </c>
       <c r="G63" t="n">
-        <v>1581.5</v>
+        <v>2084.6</v>
       </c>
       <c r="H63" t="n">
-        <v>1547.6</v>
+        <v>2113.7</v>
       </c>
       <c r="J63" t="n">
-        <v>1618.8</v>
+        <v>2031.1</v>
       </c>
       <c r="K63" t="inlineStr">
         <is>
@@ -5974,16 +5957,16 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>1.1003</v>
+        <v>1.8385</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>1.1003</v>
+        <v>1.8385</v>
       </c>
       <c r="N63" t="n">
-        <v>102310.42</v>
+        <v>100000</v>
       </c>
       <c r="O63" t="n">
-        <v>103436.14</v>
+        <v>101838.49</v>
       </c>
     </row>
     <row r="64">
@@ -5993,7 +5976,7 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -6002,25 +5985,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F64" t="n">
         <v>1</v>
       </c>
       <c r="G64" t="n">
-        <v>1559</v>
+        <v>1641.5</v>
       </c>
       <c r="H64" t="n">
-        <v>1539.5</v>
+        <v>1621</v>
       </c>
       <c r="J64" t="n">
-        <v>1586.6</v>
+        <v>1651</v>
       </c>
       <c r="K64" t="inlineStr">
         <is>
@@ -6028,16 +6011,16 @@
         </is>
       </c>
       <c r="L64" t="n">
-        <v>1.4154</v>
+        <v>0.4634</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>1.4154</v>
+        <v>0.4634</v>
       </c>
       <c r="N64" t="n">
-        <v>103436.14</v>
+        <v>101838.49</v>
       </c>
       <c r="O64" t="n">
-        <v>104900.16</v>
+        <v>102310.42</v>
       </c>
     </row>
     <row r="65">
@@ -6047,34 +6030,34 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F65" t="n">
         <v>1</v>
       </c>
       <c r="G65" t="n">
-        <v>1769.6</v>
+        <v>1581.5</v>
       </c>
       <c r="H65" t="n">
-        <v>1798.4</v>
+        <v>1547.6</v>
       </c>
       <c r="J65" t="n">
-        <v>1752.2</v>
+        <v>1618.8</v>
       </c>
       <c r="K65" t="inlineStr">
         <is>
@@ -6082,53 +6065,53 @@
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0.6042</v>
+        <v>1.1003</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0.6042</v>
+        <v>1.1003</v>
       </c>
       <c r="N65" t="n">
-        <v>104900.16</v>
+        <v>102310.42</v>
       </c>
       <c r="O65" t="n">
-        <v>105533.93</v>
+        <v>103436.14</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F66" t="n">
         <v>1</v>
       </c>
       <c r="G66" t="n">
-        <v>27907</v>
+        <v>1559</v>
       </c>
       <c r="H66" t="n">
-        <v>27965.76</v>
+        <v>1539.5</v>
       </c>
       <c r="J66" t="n">
-        <v>27760</v>
+        <v>1586.6</v>
       </c>
       <c r="K66" t="inlineStr">
         <is>
@@ -6136,26 +6119,26 @@
         </is>
       </c>
       <c r="L66" t="n">
-        <v>2.5017</v>
+        <v>1.4154</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>2.5017</v>
+        <v>1.4154</v>
       </c>
       <c r="N66" t="n">
-        <v>100000</v>
+        <v>103436.14</v>
       </c>
       <c r="O66" t="n">
-        <v>102501.7</v>
+        <v>104900.16</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Nasdaq_100_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -6176,13 +6159,13 @@
         <v>1</v>
       </c>
       <c r="G67" t="n">
-        <v>29892.8</v>
+        <v>1769.6</v>
       </c>
       <c r="H67" t="n">
-        <v>30074.01</v>
+        <v>1798.4</v>
       </c>
       <c r="J67" t="n">
-        <v>29569.5</v>
+        <v>1752.2</v>
       </c>
       <c r="K67" t="inlineStr">
         <is>
@@ -6190,26 +6173,26 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>1.7841</v>
+        <v>0.6042</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>1.7841</v>
+        <v>0.6042</v>
       </c>
       <c r="N67" t="n">
-        <v>102501.7</v>
+        <v>104900.16</v>
       </c>
       <c r="O67" t="n">
-        <v>104330.45</v>
+        <v>105533.93</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>NY_Platinum_Futures</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -6218,52 +6201,35 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>2026-04-29</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>1</v>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G68" t="n">
-        <v>7206.55</v>
+        <v>1769.6</v>
       </c>
       <c r="H68" t="n">
-        <v>7223.26</v>
-      </c>
-      <c r="J68" t="n">
-        <v>7172.5</v>
+        <v>1796.3</v>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>exit_open</t>
-        </is>
-      </c>
-      <c r="L68" t="n">
-        <v>2.0377</v>
-      </c>
-      <c r="M68" s="2" t="n">
-        <v>2.0377</v>
+          <t>open_at_end</t>
+        </is>
       </c>
       <c r="N68" t="n">
-        <v>100000</v>
+        <v>105533.93</v>
       </c>
       <c r="O68" t="n">
-        <v>102037.7</v>
+        <v>105533.93</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>S_P_500_E_mini</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -6272,25 +6238,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="F69" t="n">
         <v>1</v>
       </c>
       <c r="G69" t="n">
-        <v>7773</v>
+        <v>27907</v>
       </c>
       <c r="H69" t="n">
-        <v>7820.26</v>
+        <v>27965.76</v>
       </c>
       <c r="J69" t="n">
-        <v>7756.75</v>
+        <v>27760</v>
       </c>
       <c r="K69" t="inlineStr">
         <is>
@@ -6298,26 +6264,26 @@
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0.3438</v>
+        <v>2.5017</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.3438</v>
+        <v>2.5017</v>
       </c>
       <c r="N69" t="n">
-        <v>102037.7</v>
+        <v>100000</v>
       </c>
       <c r="O69" t="n">
-        <v>102388.55</v>
+        <v>102501.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>Nasdaq_100_E_mini</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -6326,25 +6292,25 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-01-07</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F70" t="n">
         <v>1</v>
       </c>
       <c r="G70" t="n">
-        <v>6957.43</v>
+        <v>29892.8</v>
       </c>
       <c r="H70" t="n">
-        <v>6965.7</v>
+        <v>30074.01</v>
       </c>
       <c r="J70" t="n">
-        <v>6914.11</v>
+        <v>29569.5</v>
       </c>
       <c r="K70" t="inlineStr">
         <is>
@@ -6352,26 +6318,26 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>5.2382</v>
+        <v>1.7841</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>5.2382</v>
+        <v>1.7841</v>
       </c>
       <c r="N70" t="n">
-        <v>100000</v>
+        <v>102501.7</v>
       </c>
       <c r="O70" t="n">
-        <v>105238.21</v>
+        <v>104330.45</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -6380,25 +6346,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-01-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-29</t>
         </is>
       </c>
       <c r="F71" t="n">
         <v>1</v>
       </c>
       <c r="G71" t="n">
-        <v>6982.4</v>
+        <v>7206.55</v>
       </c>
       <c r="H71" t="n">
-        <v>6988.83</v>
+        <v>7223.26</v>
       </c>
       <c r="J71" t="n">
-        <v>7002</v>
+        <v>7172.5</v>
       </c>
       <c r="K71" t="inlineStr">
         <is>
@@ -6406,26 +6372,26 @@
         </is>
       </c>
       <c r="L71" t="n">
-        <v>-3.0482</v>
-      </c>
-      <c r="M71" s="10" t="n">
-        <v>-3.0482</v>
+        <v>2.0377</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>2.0377</v>
       </c>
       <c r="N71" t="n">
-        <v>105238.21</v>
+        <v>100000</v>
       </c>
       <c r="O71" t="n">
-        <v>102030.33</v>
+        <v>102037.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>S_P_500_Index</t>
+          <t>S_P_500_E_mini</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -6434,25 +6400,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F72" t="n">
         <v>1</v>
       </c>
       <c r="G72" t="n">
-        <v>6982.4</v>
+        <v>7773</v>
       </c>
       <c r="H72" t="n">
-        <v>6992.85</v>
+        <v>7820.26</v>
       </c>
       <c r="J72" t="n">
-        <v>6947.27</v>
+        <v>7756.75</v>
       </c>
       <c r="K72" t="inlineStr">
         <is>
@@ -6460,16 +6426,16 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>3.3617</v>
+        <v>0.3438</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3.3617</v>
+        <v>0.3438</v>
       </c>
       <c r="N72" t="n">
-        <v>102030.33</v>
+        <v>102037.7</v>
       </c>
       <c r="O72" t="n">
-        <v>105460.3</v>
+        <v>102388.55</v>
       </c>
     </row>
     <row r="73">
@@ -6479,7 +6445,7 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -6488,25 +6454,25 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-01-07</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-02-03</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="F73" t="n">
         <v>1</v>
       </c>
       <c r="G73" t="n">
-        <v>6982.4</v>
+        <v>6957.43</v>
       </c>
       <c r="H73" t="n">
-        <v>6991.93</v>
+        <v>6965.7</v>
       </c>
       <c r="J73" t="n">
-        <v>6985.45</v>
+        <v>6914.11</v>
       </c>
       <c r="K73" t="inlineStr">
         <is>
@@ -6514,16 +6480,16 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>-0.32</v>
-      </c>
-      <c r="M73" s="10" t="n">
-        <v>-0.32</v>
+        <v>5.2382</v>
+      </c>
+      <c r="M73" s="2" t="n">
+        <v>5.2382</v>
       </c>
       <c r="N73" t="n">
-        <v>105460.3</v>
+        <v>100000</v>
       </c>
       <c r="O73" t="n">
-        <v>105122.79</v>
+        <v>105238.21</v>
       </c>
     </row>
     <row r="74">
@@ -6533,7 +6499,7 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -6542,12 +6508,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-02-10</t>
+          <t>2026-01-27</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -6557,10 +6523,10 @@
         <v>6982.4</v>
       </c>
       <c r="H74" t="n">
-        <v>6986.84</v>
+        <v>6988.83</v>
       </c>
       <c r="J74" t="n">
-        <v>6976.48</v>
+        <v>7002</v>
       </c>
       <c r="K74" t="inlineStr">
         <is>
@@ -6568,16 +6534,16 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>1.3333</v>
-      </c>
-      <c r="M74" s="2" t="n">
-        <v>1.3333</v>
+        <v>-3.0482</v>
+      </c>
+      <c r="M74" s="10" t="n">
+        <v>-3.0482</v>
       </c>
       <c r="N74" t="n">
-        <v>105122.79</v>
+        <v>105238.21</v>
       </c>
       <c r="O74" t="n">
-        <v>106524.42</v>
+        <v>102030.33</v>
       </c>
     </row>
     <row r="75">
@@ -6587,34 +6553,34 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="F75" t="n">
         <v>1</v>
       </c>
       <c r="G75" t="n">
-        <v>6794.4</v>
+        <v>6982.4</v>
       </c>
       <c r="H75" t="n">
-        <v>6770.77</v>
+        <v>6992.85</v>
       </c>
       <c r="J75" t="n">
-        <v>6769.03</v>
+        <v>6947.27</v>
       </c>
       <c r="K75" t="inlineStr">
         <is>
@@ -6622,26 +6588,26 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>-1.0736</v>
-      </c>
-      <c r="M75" s="10" t="n">
-        <v>-1.0736</v>
+        <v>3.3617</v>
+      </c>
+      <c r="M75" s="2" t="n">
+        <v>3.3617</v>
       </c>
       <c r="N75" t="n">
-        <v>106524.42</v>
+        <v>102030.33</v>
       </c>
       <c r="O75" t="n">
-        <v>105380.74</v>
+        <v>105460.3</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -6650,25 +6616,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-05-12</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="F76" t="n">
         <v>1</v>
       </c>
       <c r="G76" t="n">
-        <v>86.081</v>
+        <v>6982.4</v>
       </c>
       <c r="H76" t="n">
-        <v>88.001</v>
+        <v>6991.93</v>
       </c>
       <c r="J76" t="n">
-        <v>87.31999999999999</v>
+        <v>6985.45</v>
       </c>
       <c r="K76" t="inlineStr">
         <is>
@@ -6676,53 +6642,53 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>-0.6453</v>
+        <v>-0.32</v>
       </c>
       <c r="M76" s="10" t="n">
-        <v>-0.6453</v>
+        <v>-0.32</v>
       </c>
       <c r="N76" t="n">
-        <v>100000</v>
+        <v>105460.3</v>
       </c>
       <c r="O76" t="n">
-        <v>99354.69</v>
+        <v>105122.79</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Silver_Futures_COMEX</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="F77" t="n">
         <v>1</v>
       </c>
       <c r="G77" t="n">
-        <v>73.84399999999999</v>
+        <v>6982.4</v>
       </c>
       <c r="H77" t="n">
-        <v>71.999</v>
+        <v>6986.84</v>
       </c>
       <c r="J77" t="n">
-        <v>75.565</v>
+        <v>6976.48</v>
       </c>
       <c r="K77" t="inlineStr">
         <is>
@@ -6730,53 +6696,53 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0.9328</v>
+        <v>1.3333</v>
       </c>
       <c r="M77" s="2" t="n">
-        <v>0.9328</v>
+        <v>1.3333</v>
       </c>
       <c r="N77" t="n">
-        <v>99354.69</v>
+        <v>105122.79</v>
       </c>
       <c r="O77" t="n">
-        <v>100281.46</v>
+        <v>106524.42</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sugar_World_CSCE_Futures</t>
+          <t>S_P_500_Index</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="F78" t="n">
         <v>1</v>
       </c>
       <c r="G78" t="n">
-        <v>15</v>
+        <v>6794.4</v>
       </c>
       <c r="H78" t="n">
-        <v>15.26</v>
+        <v>6770.77</v>
       </c>
       <c r="J78" t="n">
-        <v>15</v>
+        <v>6769.03</v>
       </c>
       <c r="K78" t="inlineStr">
         <is>
@@ -6784,22 +6750,22 @@
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" s="4" t="n">
-        <v>0</v>
+        <v>-1.0736</v>
+      </c>
+      <c r="M78" s="10" t="n">
+        <v>-1.0736</v>
       </c>
       <c r="N78" t="n">
-        <v>100000</v>
+        <v>106524.42</v>
       </c>
       <c r="O78" t="n">
-        <v>100000</v>
+        <v>105380.74</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Teucrium_Wheat_Fund</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B79" t="n">
@@ -6812,25 +6778,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-01-29</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="F79" t="n">
         <v>1</v>
       </c>
       <c r="G79" t="n">
-        <v>20.89</v>
+        <v>86.081</v>
       </c>
       <c r="H79" t="n">
-        <v>21.07</v>
+        <v>88.001</v>
       </c>
       <c r="J79" t="n">
-        <v>21.08</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="K79" t="inlineStr">
         <is>
@@ -6838,53 +6804,53 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>-1.0556</v>
+        <v>-0.6453</v>
       </c>
       <c r="M79" s="10" t="n">
-        <v>-1.0556</v>
+        <v>-0.6453</v>
       </c>
       <c r="N79" t="n">
         <v>100000</v>
       </c>
       <c r="O79" t="n">
-        <v>98944.44</v>
+        <v>99354.69</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Silver_Futures_COMEX</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-03-04</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F80" t="n">
         <v>1</v>
       </c>
       <c r="G80" t="n">
-        <v>0.8614000000000001</v>
+        <v>73.84399999999999</v>
       </c>
       <c r="H80" t="n">
-        <v>0.8637</v>
+        <v>71.999</v>
       </c>
       <c r="J80" t="n">
-        <v>0.8594000000000001</v>
+        <v>75.565</v>
       </c>
       <c r="K80" t="inlineStr">
         <is>
@@ -6892,26 +6858,26 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0.8696</v>
+        <v>0.9328</v>
       </c>
       <c r="M80" s="2" t="n">
-        <v>0.8696</v>
+        <v>0.9328</v>
       </c>
       <c r="N80" t="n">
-        <v>100000</v>
+        <v>99354.69</v>
       </c>
       <c r="O80" t="n">
-        <v>100869.57</v>
+        <v>100281.46</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Sugar_World_CSCE_Futures</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -6920,25 +6886,25 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-03-06</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F81" t="n">
         <v>1</v>
       </c>
       <c r="G81" t="n">
-        <v>0.8614000000000001</v>
+        <v>15</v>
       </c>
       <c r="H81" t="n">
-        <v>0.8658</v>
+        <v>15.26</v>
       </c>
       <c r="J81" t="n">
-        <v>0.8602</v>
+        <v>15</v>
       </c>
       <c r="K81" t="inlineStr">
         <is>
@@ -6946,76 +6912,76 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0.2727</v>
-      </c>
-      <c r="M81" s="2" t="n">
-        <v>0.2727</v>
+        <v>0</v>
+      </c>
+      <c r="M81" s="4" t="n">
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>100869.57</v>
+        <v>100000</v>
       </c>
       <c r="O81" t="n">
-        <v>101144.66</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>USD_EUR_Cross_Rate</t>
+          <t>Teucrium_Wheat_Fund</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-28</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-01-29</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.8467</v>
+        <v>20.89</v>
       </c>
       <c r="H82" t="n">
-        <v>0.8436</v>
+        <v>21.07</v>
       </c>
       <c r="J82" t="n">
-        <v>0.8498</v>
+        <v>21.08</v>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>data_end</t>
+          <t>exit_open</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1</v>
-      </c>
-      <c r="M82" s="2" t="n">
-        <v>1</v>
+        <v>-1.0556</v>
+      </c>
+      <c r="M82" s="10" t="n">
+        <v>-1.0556</v>
       </c>
       <c r="N82" t="n">
-        <v>101144.66</v>
+        <v>100000</v>
       </c>
       <c r="O82" t="n">
-        <v>102156.11</v>
+        <v>98944.44</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B83" t="n">
@@ -7028,25 +6994,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-04</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-02-12</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="F83" t="n">
         <v>1</v>
       </c>
       <c r="G83" t="n">
-        <v>116.5</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H83" t="n">
-        <v>116.79</v>
+        <v>0.8637</v>
       </c>
       <c r="J83" t="n">
-        <v>116.15</v>
+        <v>0.8594000000000001</v>
       </c>
       <c r="K83" t="inlineStr">
         <is>
@@ -7054,22 +7020,22 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>1.2069</v>
+        <v>0.8696</v>
       </c>
       <c r="M83" s="2" t="n">
-        <v>1.2069</v>
+        <v>0.8696</v>
       </c>
       <c r="N83" t="n">
         <v>100000</v>
       </c>
       <c r="O83" t="n">
-        <v>101206.9</v>
+        <v>100869.57</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B84" t="n">
@@ -7082,25 +7048,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-06</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="F84" t="n">
         <v>1</v>
       </c>
       <c r="G84" t="n">
-        <v>118.02</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="H84" t="n">
-        <v>118.16</v>
+        <v>0.8658</v>
       </c>
       <c r="J84" t="n">
-        <v>117.9</v>
+        <v>0.8602</v>
       </c>
       <c r="K84" t="inlineStr">
         <is>
@@ -7108,22 +7074,22 @@
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0.8571</v>
+        <v>0.2727</v>
       </c>
       <c r="M84" s="2" t="n">
-        <v>0.8571</v>
+        <v>0.2727</v>
       </c>
       <c r="N84" t="n">
-        <v>101206.9</v>
+        <v>100869.57</v>
       </c>
       <c r="O84" t="n">
-        <v>102074.38</v>
+        <v>101144.66</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>US_30_Year_T_Bond_Futures_CBOT</t>
+          <t>USD_EUR_Cross_Rate</t>
         </is>
       </c>
       <c r="B85" t="n">
@@ -7131,53 +7097,53 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="F85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85" t="n">
-        <v>118.08</v>
+        <v>0.8467</v>
       </c>
       <c r="H85" t="n">
-        <v>118.16</v>
+        <v>0.8436</v>
       </c>
       <c r="J85" t="n">
-        <v>117.87</v>
+        <v>0.8498</v>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>exit_open</t>
+          <t>data_end</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>2.625</v>
+        <v>1</v>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2.625</v>
+        <v>1</v>
       </c>
       <c r="N85" t="n">
-        <v>102074.38</v>
+        <v>101144.66</v>
       </c>
       <c r="O85" t="n">
-        <v>104753.84</v>
+        <v>102156.11</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B86" t="n">
@@ -7185,30 +7151,30 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="F86" t="n">
         <v>1</v>
       </c>
       <c r="G86" t="n">
-        <v>97.81399999999999</v>
+        <v>116.5</v>
       </c>
       <c r="H86" t="n">
-        <v>97.569</v>
+        <v>116.79</v>
       </c>
       <c r="J86" t="n">
-        <v>98</v>
+        <v>116.15</v>
       </c>
       <c r="K86" t="inlineStr">
         <is>
@@ -7216,22 +7182,22 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0.7592</v>
+        <v>1.2069</v>
       </c>
       <c r="M86" s="2" t="n">
-        <v>0.7592</v>
+        <v>1.2069</v>
       </c>
       <c r="N86" t="n">
         <v>100000</v>
       </c>
       <c r="O86" t="n">
-        <v>100759.18</v>
+        <v>101206.9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B87" t="n">
@@ -7239,30 +7205,30 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>long</t>
+          <t>short</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="F87" t="n">
         <v>1</v>
       </c>
       <c r="G87" t="n">
-        <v>97.714</v>
+        <v>118.02</v>
       </c>
       <c r="H87" t="n">
-        <v>97.46899999999999</v>
+        <v>118.16</v>
       </c>
       <c r="J87" t="n">
-        <v>97.905</v>
+        <v>117.9</v>
       </c>
       <c r="K87" t="inlineStr">
         <is>
@@ -7270,22 +7236,22 @@
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0.7796</v>
+        <v>0.8571</v>
       </c>
       <c r="M87" s="2" t="n">
-        <v>0.7796</v>
+        <v>0.8571</v>
       </c>
       <c r="N87" t="n">
-        <v>100759.18</v>
+        <v>101206.9</v>
       </c>
       <c r="O87" t="n">
-        <v>101544.69</v>
+        <v>102074.38</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>US_Dollar_Index_Futures</t>
+          <t>US_30_Year_T_Bond_Futures_CBOT</t>
         </is>
       </c>
       <c r="B88" t="n">
@@ -7298,25 +7264,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="F88" t="n">
         <v>1</v>
       </c>
       <c r="G88" t="n">
-        <v>99.376</v>
+        <v>118.08</v>
       </c>
       <c r="H88" t="n">
-        <v>99.571</v>
+        <v>118.16</v>
       </c>
       <c r="J88" t="n">
-        <v>99.095</v>
+        <v>117.87</v>
       </c>
       <c r="K88" t="inlineStr">
         <is>
@@ -7324,16 +7290,16 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>1.441</v>
+        <v>2.625</v>
       </c>
       <c r="M88" s="2" t="n">
-        <v>1.441</v>
+        <v>2.625</v>
       </c>
       <c r="N88" t="n">
-        <v>101544.69</v>
+        <v>102074.38</v>
       </c>
       <c r="O88" t="n">
-        <v>103007.98</v>
+        <v>104753.84</v>
       </c>
     </row>
     <row r="89">
@@ -7343,34 +7309,34 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="F89" t="n">
         <v>1</v>
       </c>
       <c r="G89" t="n">
-        <v>99.246</v>
+        <v>97.81399999999999</v>
       </c>
       <c r="H89" t="n">
-        <v>99.501</v>
+        <v>97.569</v>
       </c>
       <c r="J89" t="n">
-        <v>98.87</v>
+        <v>98</v>
       </c>
       <c r="K89" t="inlineStr">
         <is>
@@ -7378,16 +7344,16 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>1.4745</v>
+        <v>0.7592</v>
       </c>
       <c r="M89" s="2" t="n">
-        <v>1.4745</v>
+        <v>0.7592</v>
       </c>
       <c r="N89" t="n">
-        <v>103007.98</v>
+        <v>100000</v>
       </c>
       <c r="O89" t="n">
-        <v>104526.84</v>
+        <v>100759.18</v>
       </c>
     </row>
     <row r="90">
@@ -7397,34 +7363,34 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>short</t>
+          <t>long</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="F90" t="n">
         <v>1</v>
       </c>
       <c r="G90" t="n">
-        <v>100.066</v>
+        <v>97.714</v>
       </c>
       <c r="H90" t="n">
-        <v>100.201</v>
+        <v>97.46899999999999</v>
       </c>
       <c r="J90" t="n">
-        <v>100.045</v>
+        <v>97.905</v>
       </c>
       <c r="K90" t="inlineStr">
         <is>
@@ -7432,16 +7398,16 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0.1556</v>
+        <v>0.7796</v>
       </c>
       <c r="M90" s="2" t="n">
-        <v>0.1556</v>
+        <v>0.7796</v>
       </c>
       <c r="N90" t="n">
-        <v>104526.84</v>
+        <v>100759.18</v>
       </c>
       <c r="O90" t="n">
-        <v>104689.44</v>
+        <v>101544.69</v>
       </c>
     </row>
     <row r="91">
@@ -7451,7 +7417,7 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -7460,25 +7426,25 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="F91" t="n">
         <v>1</v>
       </c>
       <c r="G91" t="n">
-        <v>100.066</v>
+        <v>99.376</v>
       </c>
       <c r="H91" t="n">
-        <v>100.316</v>
+        <v>99.571</v>
       </c>
       <c r="J91" t="n">
-        <v>99.45999999999999</v>
+        <v>99.095</v>
       </c>
       <c r="K91" t="inlineStr">
         <is>
@@ -7486,16 +7452,16 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>2.424</v>
+        <v>1.441</v>
       </c>
       <c r="M91" s="2" t="n">
-        <v>2.424</v>
+        <v>1.441</v>
       </c>
       <c r="N91" t="n">
-        <v>104689.44</v>
+        <v>101544.69</v>
       </c>
       <c r="O91" t="n">
-        <v>107227.11</v>
+        <v>103007.98</v>
       </c>
     </row>
     <row r="92">
@@ -7505,7 +7471,7 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -7514,25 +7480,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="F92" t="n">
         <v>1</v>
       </c>
       <c r="G92" t="n">
-        <v>100.066</v>
+        <v>99.246</v>
       </c>
       <c r="H92" t="n">
-        <v>100.361</v>
+        <v>99.501</v>
       </c>
       <c r="J92" t="n">
-        <v>100.15</v>
+        <v>98.87</v>
       </c>
       <c r="K92" t="inlineStr">
         <is>
@@ -7540,16 +7506,16 @@
         </is>
       </c>
       <c r="L92" t="n">
-        <v>-0.2847</v>
-      </c>
-      <c r="M92" s="10" t="n">
-        <v>-0.2847</v>
+        <v>1.4745</v>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>1.4745</v>
       </c>
       <c r="N92" t="n">
-        <v>107227.11</v>
+        <v>103007.98</v>
       </c>
       <c r="O92" t="n">
-        <v>106921.79</v>
+        <v>104526.84</v>
       </c>
     </row>
     <row r="93">
@@ -7559,7 +7525,7 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -7568,25 +7534,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F93" t="n">
         <v>1</v>
       </c>
       <c r="G93" t="n">
-        <v>100.621</v>
+        <v>100.066</v>
       </c>
       <c r="H93" t="n">
-        <v>100.911</v>
+        <v>100.201</v>
       </c>
       <c r="J93" t="n">
-        <v>100.7</v>
+        <v>100.045</v>
       </c>
       <c r="K93" t="inlineStr">
         <is>
@@ -7594,16 +7560,16 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>-0.2724</v>
-      </c>
-      <c r="M93" s="10" t="n">
-        <v>-0.2724</v>
+        <v>0.1556</v>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>0.1556</v>
       </c>
       <c r="N93" t="n">
-        <v>106921.79</v>
+        <v>104526.84</v>
       </c>
       <c r="O93" t="n">
-        <v>106630.52</v>
+        <v>104689.44</v>
       </c>
     </row>
     <row r="94">
@@ -7613,7 +7579,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -7622,25 +7588,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-11</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="F94" t="n">
         <v>1</v>
       </c>
       <c r="G94" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H94" t="n">
-        <v>101.526</v>
+        <v>100.316</v>
       </c>
       <c r="J94" t="n">
-        <v>101.295</v>
+        <v>99.45999999999999</v>
       </c>
       <c r="K94" t="inlineStr">
         <is>
@@ -7648,16 +7614,16 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>1.0087</v>
+        <v>2.424</v>
       </c>
       <c r="M94" s="2" t="n">
-        <v>1.0087</v>
+        <v>2.424</v>
       </c>
       <c r="N94" t="n">
-        <v>106630.52</v>
+        <v>104689.44</v>
       </c>
       <c r="O94" t="n">
-        <v>107706.09</v>
+        <v>107227.11</v>
       </c>
     </row>
     <row r="95">
@@ -7667,7 +7633,7 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -7676,25 +7642,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F95" t="n">
         <v>1</v>
       </c>
       <c r="G95" t="n">
-        <v>101.411</v>
+        <v>100.066</v>
       </c>
       <c r="H95" t="n">
-        <v>101.491</v>
+        <v>100.361</v>
       </c>
       <c r="J95" t="n">
-        <v>101.29</v>
+        <v>100.15</v>
       </c>
       <c r="K95" t="inlineStr">
         <is>
@@ -7702,26 +7668,26 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.5125</v>
-      </c>
-      <c r="M95" s="2" t="n">
-        <v>1.5125</v>
+        <v>-0.2847</v>
+      </c>
+      <c r="M95" s="10" t="n">
+        <v>-0.2847</v>
       </c>
       <c r="N95" t="n">
-        <v>107706.09</v>
+        <v>107227.11</v>
       </c>
       <c r="O95" t="n">
-        <v>109335.15</v>
+        <v>106921.79</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>United_States_Oil_Fund_LP</t>
+          <t>US_Dollar_Index_Futures</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -7730,25 +7696,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="F96" t="n">
         <v>1</v>
       </c>
       <c r="G96" t="n">
-        <v>121.72</v>
+        <v>100.621</v>
       </c>
       <c r="H96" t="n">
-        <v>123.03</v>
+        <v>100.911</v>
       </c>
       <c r="J96" t="n">
-        <v>113.29</v>
+        <v>100.7</v>
       </c>
       <c r="K96" t="inlineStr">
         <is>
@@ -7756,69 +7722,231 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>6.4351</v>
-      </c>
-      <c r="M96" s="2" t="n">
-        <v>6.4351</v>
+        <v>-0.2724</v>
+      </c>
+      <c r="M96" s="10" t="n">
+        <v>-0.2724</v>
       </c>
       <c r="N96" t="n">
-        <v>100000</v>
+        <v>106921.79</v>
       </c>
       <c r="O96" t="n">
-        <v>106435.11</v>
+        <v>106630.52</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>9</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H97" t="n">
+        <v>101.526</v>
+      </c>
+      <c r="J97" t="n">
+        <v>101.295</v>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>1.0087</v>
+      </c>
+      <c r="M97" s="2" t="n">
+        <v>1.0087</v>
+      </c>
+      <c r="N97" t="n">
+        <v>106630.52</v>
+      </c>
+      <c r="O97" t="n">
+        <v>107706.09</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>10</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="n">
+        <v>101.411</v>
+      </c>
+      <c r="H98" t="n">
+        <v>101.491</v>
+      </c>
+      <c r="J98" t="n">
+        <v>101.29</v>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>1.5125</v>
+      </c>
+      <c r="M98" s="2" t="n">
+        <v>1.5125</v>
+      </c>
+      <c r="N98" t="n">
+        <v>107706.09</v>
+      </c>
+      <c r="O98" t="n">
+        <v>109335.15</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
           <t>United_States_Oil_Fund_LP</t>
         </is>
       </c>
-      <c r="B97" t="n">
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2026-03-20</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="n">
+        <v>121.72</v>
+      </c>
+      <c r="H99" t="n">
+        <v>123.03</v>
+      </c>
+      <c r="J99" t="n">
+        <v>113.29</v>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>6.4351</v>
+      </c>
+      <c r="M99" s="2" t="n">
+        <v>6.4351</v>
+      </c>
+      <c r="N99" t="n">
+        <v>100000</v>
+      </c>
+      <c r="O99" t="n">
+        <v>106435.11</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>United_States_Oil_Fund_LP</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
         <v>2</v>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C100" t="inlineStr">
         <is>
           <t>short</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr">
+      <c r="D100" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E100" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="F97" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" t="n">
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="n">
         <v>130.16</v>
       </c>
-      <c r="H97" t="n">
+      <c r="H100" t="n">
         <v>130.94</v>
       </c>
-      <c r="J97" t="n">
+      <c r="J100" t="n">
         <v>124.86</v>
       </c>
-      <c r="K97" t="inlineStr">
-        <is>
-          <t>exit_open</t>
-        </is>
-      </c>
-      <c r="L97" t="n">
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>exit_open</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
         <v>6.7949</v>
       </c>
-      <c r="M97" s="2" t="n">
+      <c r="M100" s="2" t="n">
         <v>6.7949</v>
       </c>
-      <c r="N97" t="n">
+      <c r="N100" t="n">
         <v>106435.11</v>
       </c>
-      <c r="O97" t="n">
+      <c r="O100" t="n">
         <v>113667.24</v>
       </c>
     </row>
